--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\AUTOSERVICIOS MAYORISTAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12180" windowHeight="9495"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,7 +225,7 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/junio de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/julio de 2026</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="24" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B88" s="31">
         <v>-12.36166231246737</v>
@@ -2518,41 +2518,49 @@
         <v>-20.682735712881861</v>
       </c>
     </row>
-    <row r="114" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="37" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="31">
+        <v>-16.989147873582265</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B114" s="37"/>
-    </row>
-    <row r="115" spans="1:6" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="35" t="s">
+      <c r="B115" s="37"/>
+    </row>
+    <row r="116" spans="1:6" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B115" s="35"/>
-    </row>
-    <row r="116" spans="1:6" s="15" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="35" t="s">
+      <c r="B116" s="35"/>
+    </row>
+    <row r="117" spans="1:6" s="15" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B116" s="35"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="117" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="33" t="s">
+      <c r="B117" s="35"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B117" s="33"/>
+      <c r="B118" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="A115:B115"/>
     <mergeCell ref="A116:B116"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -2610,7 +2618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2619,7 +2627,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -2635,7 +2643,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
@@ -2652,7 +2660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -2660,7 +2668,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2668,7 +2676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -2684,7 +2692,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>

--- a/idecba/autoservicios.xlsx
+++ b/idecba/autoservicios.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\COMERCIO INTERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972E9A1A-F095-4C33-8EBF-F0D432A84C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AC_M_01" sheetId="1" r:id="rId1"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="59">
   <si>
     <t>Período</t>
   </si>
@@ -225,13 +226,13 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/julio de 2026</t>
+    <t>Ventas a valores constantes en autoservicios mayoristas. Variación interanual (%). Ciudad de Buenos Aires. Años 2018/agosto de 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -1049,57 +1050,57 @@
     </xf>
   </cellXfs>
   <cellStyles count="51">
-    <cellStyle name="20% - Énfasis1 2" xfId="1"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="2"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="3"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="4"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="5"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="6"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="7"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="8"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="9"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="10"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="11"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="12"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="13"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="14"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="15"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="16"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="17"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="18"/>
-    <cellStyle name="Buena 2" xfId="19"/>
-    <cellStyle name="Cálculo 2" xfId="20"/>
-    <cellStyle name="Celda de comprobación 2" xfId="21"/>
-    <cellStyle name="Celda vinculada 2" xfId="22"/>
-    <cellStyle name="Encabezado 4 2" xfId="23"/>
-    <cellStyle name="Énfasis1 2" xfId="24"/>
-    <cellStyle name="Énfasis2 2" xfId="25"/>
-    <cellStyle name="Énfasis3 2" xfId="26"/>
-    <cellStyle name="Énfasis4 2" xfId="27"/>
-    <cellStyle name="Énfasis5 2" xfId="28"/>
-    <cellStyle name="Énfasis6 2" xfId="29"/>
-    <cellStyle name="Entrada 2" xfId="30"/>
-    <cellStyle name="Euro" xfId="31"/>
-    <cellStyle name="Incorrecto 2" xfId="32"/>
-    <cellStyle name="mio" xfId="33"/>
-    <cellStyle name="Neutral 2" xfId="34"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Buena 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Cálculo 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Celda vinculada 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Encabezado 4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Énfasis1 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Énfasis2 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Énfasis3 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Énfasis4 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Énfasis5 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Énfasis6 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Entrada 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Euro" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Incorrecto 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="mio" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Neutral 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="35"/>
-    <cellStyle name="Normal 2 2" xfId="36"/>
-    <cellStyle name="Normal 2 3" xfId="50"/>
-    <cellStyle name="Normal 3" xfId="37"/>
-    <cellStyle name="Normal 6" xfId="49"/>
-    <cellStyle name="Normal_Cuadro6comercio24" xfId="38"/>
-    <cellStyle name="Notas 2" xfId="39"/>
-    <cellStyle name="Pato" xfId="40"/>
-    <cellStyle name="Salida 2" xfId="41"/>
-    <cellStyle name="Texto de advertencia 2" xfId="42"/>
-    <cellStyle name="Texto explicativo 2" xfId="43"/>
-    <cellStyle name="Título 1 2" xfId="44"/>
-    <cellStyle name="Título 2 2" xfId="45"/>
-    <cellStyle name="Título 3 2" xfId="46"/>
-    <cellStyle name="Título 4" xfId="47"/>
-    <cellStyle name="Total 2" xfId="48"/>
+    <cellStyle name="Normal 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 2 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 2 3" xfId="50" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 3" xfId="37" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 6" xfId="49" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal_Cuadro6comercio24" xfId="38" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Notas 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Pato" xfId="40" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Salida 2" xfId="41" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Título 1 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Título 2 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Título 3 2" xfId="46" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Título 4" xfId="47" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Total 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1115,9 +1116,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1155,9 +1156,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1192,7 +1193,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1227,7 +1228,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1400,16 +1401,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H119"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="24" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="24"/>
+    <col min="1" max="1" width="14.109375" style="24" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="24" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>58</v>
       </c>
@@ -1429,7 +1430,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="12" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>2018</v>
       </c>
@@ -1550,7 +1551,7 @@
       <c r="D15" s="29"/>
       <c r="E15" s="32"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>2019</v>
       </c>
@@ -1680,7 +1681,7 @@
       <c r="D28" s="29"/>
       <c r="E28" s="32"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>2020</v>
       </c>
@@ -1810,7 +1811,7 @@
       <c r="D41" s="29"/>
       <c r="E41" s="32"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>2021</v>
       </c>
@@ -1940,7 +1941,7 @@
       <c r="D54" s="29"/>
       <c r="E54" s="32"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>2022</v>
       </c>
@@ -2070,7 +2071,7 @@
       <c r="D67" s="29"/>
       <c r="E67" s="32"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>2023</v>
       </c>
@@ -2200,7 +2201,7 @@
       <c r="D80" s="29"/>
       <c r="E80" s="32"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>56</v>
       </c>
@@ -2282,7 +2283,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="24" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B89" s="31">
         <v>-5.4533665063562502</v>
@@ -2330,7 +2331,7 @@
       <c r="D93" s="29"/>
       <c r="E93" s="32"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>57</v>
       </c>
@@ -2460,7 +2461,7 @@
       <c r="D106" s="29"/>
       <c r="E106" s="32"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="12" x14ac:dyDescent="0.25">
       <c r="A107" s="14">
         <v>2026</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="31">
-        <v>-20.169242462508862</v>
+        <v>-20.169242462508898</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -2491,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="B110" s="31">
-        <v>-21.848546508004119</v>
+        <v>-21.848546508004151</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2499,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="B111" s="31">
-        <v>-19.010927477164831</v>
+        <v>-19.010927477164842</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -2515,7 +2516,7 @@
         <v>7</v>
       </c>
       <c r="B113" s="31">
-        <v>-20.682735712881861</v>
+        <v>-20.682735712881872</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
@@ -2523,44 +2524,52 @@
         <v>8</v>
       </c>
       <c r="B114" s="31">
-        <v>-16.989147873582265</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="37" t="s">
+        <v>-16.989147873582301</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" s="31">
+        <v>-19.348813508796749</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B115" s="37"/>
-    </row>
-    <row r="116" spans="1:6" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="35" t="s">
+      <c r="B116" s="37"/>
+    </row>
+    <row r="117" spans="1:6" s="15" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B116" s="35"/>
-    </row>
-    <row r="117" spans="1:6" s="15" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="35" t="s">
+      <c r="B117" s="35"/>
+    </row>
+    <row r="118" spans="1:6" s="15" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B117" s="35"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="118" spans="1:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="33" t="s">
+      <c r="B118" s="35"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+    </row>
+    <row r="119" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B118" s="33"/>
+      <c r="B119" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="A116:B116"/>
     <mergeCell ref="A117:B117"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A116:B116"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -2570,23 +2579,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="47.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="39"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2594,7 +2603,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -2602,7 +2611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -2610,7 +2619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -2618,7 +2627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2627,7 +2636,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -2635,7 +2644,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>18</v>
       </c>
@@ -2643,7 +2652,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
@@ -2652,7 +2661,7 @@
       </c>
       <c r="C9" s="12"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
@@ -2660,7 +2669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -2668,7 +2677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2676,7 +2685,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -2684,7 +2693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
@@ -2692,7 +2701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
